--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_antofagasta_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_antofagasta_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:17</t>
+    <t xml:space="preserve">2026-09-29 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_antofagasta_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_antofagasta_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:06</t>
+    <t xml:space="preserve">2026-09-29 18:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>-6.27</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>63.19</v>
+        <v>63.18</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>69.46</v>
@@ -504,10 +504,10 @@
         <v>-7.67</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36.47</v>
+        <v>36.46</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>44.14</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="4">
@@ -518,10 +518,10 @@
         <v>-13.38</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.49</v>
+        <v>45.48</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>58.87</v>
+        <v>58.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_antofagasta_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_antofagasta_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:44</t>
+    <t xml:space="preserve">2026-10-05 04:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>-6.27</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>63.18</v>
+        <v>63.19</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>69.46</v>
@@ -504,10 +504,10 @@
         <v>-7.67</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36.46</v>
+        <v>36.47</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>44.13</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="4">
@@ -518,10 +518,10 @@
         <v>-13.38</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45.48</v>
+        <v>45.49</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>58.86</v>
+        <v>58.87</v>
       </c>
     </row>
   </sheetData>
